--- a/excel/condition_template.xlsx
+++ b/excel/condition_template.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\study\src\github.com\fish-tennis\gserver\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -69,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>CfgId</t>
   </si>
@@ -133,6 +138,12 @@
   </si>
   <si>
     <t>活动天数&gt;=X</t>
+  </si>
+  <si>
+    <t>CreateDayCount</t>
+  </si>
+  <si>
+    <t>创角天数&gt;=X</t>
   </si>
 </sst>
 </file>
@@ -1293,8 +1304,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.5" customWidth="1"/>
@@ -1328,7 +1339,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1409,6 +1420,26 @@
       </c>
       <c r="G5" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
